--- a/backtest_runs/20260410_193731/filter/BELA/BELA.xlsx
+++ b/backtest_runs/20260410_193731/filter/BELA/BELA.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>-6155.520000000006</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>93844.48</v>
@@ -633,7 +633,7 @@
         <v>-6787.559999999997</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>87056.92</v>
@@ -679,7 +679,7 @@
         <v>-6732.599999999998</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>80324.32000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2514.419999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>103888.42</v>
@@ -1231,7 +1231,7 @@
         <v>-10717.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>93171.22000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-7639.440000000003</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>85531.78000000001</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>85531.78000000001</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>85531.78000000001</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>90725.50000000001</v>
